--- a/outputs/sens/welfare_comparison.xlsx
+++ b/outputs/sens/welfare_comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\outputs\sens\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FE0890-5000-4F41-A71E-468870FC77BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D62893-B045-49BD-9C4E-3EC67388A7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-930" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="welfare" sheetId="1" r:id="rId1"/>
@@ -493,7 +493,7 @@
   <dimension ref="A1:K217"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.90625" customWidth="1"/>
+    <col min="2" max="2" width="40.26953125" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="16.81640625" customWidth="1"/>
     <col min="7" max="7" width="15.36328125" customWidth="1"/>
